--- a/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,22; 44,9</t>
+          <t>28,3; 44,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,48; 49,08</t>
+          <t>31,85; 49,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 30,84</t>
+          <t>17,04; 31,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,62; 57,42</t>
+          <t>39,49; 57,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 44,48</t>
+          <t>28,58; 44,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 35,52</t>
+          <t>20,99; 34,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,86; 47,69</t>
+          <t>36,21; 48,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 43,99</t>
+          <t>32,02; 43,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 31,22</t>
+          <t>21,03; 31,62</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 46,99</t>
+          <t>30,46; 47,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 44,54</t>
+          <t>28,65; 44,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 29,46</t>
+          <t>15,73; 29,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,8; 52,12</t>
+          <t>35,94; 52,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,2; 48,96</t>
+          <t>33,2; 48,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 32,69</t>
+          <t>17,31; 34,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,79; 47,14</t>
+          <t>34,59; 46,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,25; 44,38</t>
+          <t>33,59; 44,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 28,92</t>
+          <t>18,6; 28,85</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,3; 38,77</t>
+          <t>22,56; 37,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,97; 44,86</t>
+          <t>25,5; 42,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 20,31</t>
+          <t>5,93; 22,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,67; 37,99</t>
+          <t>21,14; 36,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,2; 46,61</t>
+          <t>28,65; 46,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 20,25</t>
+          <t>6,42; 20,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,08; 35,22</t>
+          <t>23,03; 35,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 42,25</t>
+          <t>30,16; 42,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 18,18</t>
+          <t>7,25; 18,06</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,57; 32,29</t>
+          <t>21,46; 31,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 36,64</t>
+          <t>26,72; 36,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,46</t>
+          <t>8,92; 19,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 34,73</t>
+          <t>24,18; 34,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 31,03</t>
+          <t>21,5; 31,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 27,51</t>
+          <t>16,1; 27,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 31,04</t>
+          <t>24,19; 31,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 32,33</t>
+          <t>25,54; 32,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,48</t>
+          <t>13,47; 21,58</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 28,39</t>
+          <t>16,88; 29,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 24,93</t>
+          <t>14,22; 25,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 17,51</t>
+          <t>7,29; 17,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,81; 34,56</t>
+          <t>22,21; 35,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 25,72</t>
+          <t>13,67; 24,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 39,74</t>
+          <t>10,25; 34,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 29,69</t>
+          <t>21,24; 30,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,18; 23,16</t>
+          <t>15,4; 23,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,58; 28,42</t>
+          <t>10,37; 26,99</t>
         </is>
       </c>
     </row>
@@ -1225,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,83; 32,72</t>
+          <t>13,07; 31,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,15; 38,07</t>
+          <t>18,93; 37,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 26,63</t>
+          <t>9,16; 26,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,79; 31,94</t>
+          <t>15,75; 30,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,39; 28,82</t>
+          <t>13,4; 30,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 23,29</t>
+          <t>7,53; 24,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,9; 29,05</t>
+          <t>16,8; 28,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 30,19</t>
+          <t>18,05; 30,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,22; 21,66</t>
+          <t>10,04; 21,61</t>
         </is>
       </c>
     </row>
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,86; 31,41</t>
+          <t>25,72; 31,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 33,86</t>
+          <t>28,21; 33,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 19,01</t>
+          <t>13,37; 18,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,99; 35,66</t>
+          <t>29,88; 35,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,89</t>
+          <t>26,4; 31,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 25,4</t>
+          <t>17,62; 25,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,66; 32,72</t>
+          <t>28,78; 32,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,89; 31,92</t>
+          <t>27,84; 31,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,31; 21,05</t>
+          <t>16,29; 21,05</t>
         </is>
       </c>
     </row>
@@ -1402,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33517</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24319</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43633</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37828</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75733</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>69351</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>62146</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>25452; 39581</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26461; 41082</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17801; 32403</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35447; 51261</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28306; 43968</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>28385; 47205</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>65075; 86580</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>58318; 79626</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>50418; 75811</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>35870</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37800</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42319</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23130</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78189</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>84020</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>44122</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>28172; 43740</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29916; 46158</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14894; 28385</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>34780; 50733</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>37208; 54382</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>16541; 32533</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>65459; 88052</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>72714; 96674</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>35396; 54893</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25491</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21166</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5819</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25007</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27900</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7784</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50498</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>49065</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13603</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>19441; 32539</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15772; 26495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3076; 11890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18366; 31926</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21423; 34774</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4097; 12946</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>39847; 61723</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>41199; 58306</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8392; 20897</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>54211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70557</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29851</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66066</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54019</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45826</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>120277</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>124576</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>75678</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>44235; 64417</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59747; 81837</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19439; 41471</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55015; 78242</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>44890; 65006</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>35145; 60116</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>104905; 136242</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>110413; 141327</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>58744; 94131</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>33379</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25732</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13899</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39979</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26708</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29140</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73358</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>52440</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>43039</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>24904; 42822</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19268; 34450</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8704; 20733</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31185; 49140</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19475; 35045</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16667; 55901</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>61156; 86669</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>42816; 64707</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>29250; 76113</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>11251</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17178</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11541</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17031</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13730</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9914</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>28282</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>30908</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>21455</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6955; 16581</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11562; 23205</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6311; 18101</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11660; 22824</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9088; 20841</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5423; 17423</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>21382; 36682</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>23274; 39563</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>14149; 30449</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>192302</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>205949</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>106420</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>234035</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>204410</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>153623</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>426337</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>410359</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>260043</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>173752; 212756</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>188911; 225511</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>87890; 123198</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>213764; 255806</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>186066; 224581</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>131688; 189080</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>400285; 455411</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>382660; 437949</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>228763; 295724</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,3; 44,01</t>
+          <t>26,63; 44,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,85; 49,44</t>
+          <t>31,58; 49,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,04; 31,02</t>
+          <t>17,68; 31,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39,49; 57,11</t>
+          <t>40,03; 57,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,58; 44,4</t>
+          <t>28,46; 43,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,99; 34,9</t>
+          <t>19,82; 35,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,21; 48,18</t>
+          <t>35,79; 48,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,02; 43,72</t>
+          <t>32,93; 44,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 31,62</t>
+          <t>21,01; 31,46</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,46; 47,3</t>
+          <t>31,15; 48,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,65; 44,2</t>
+          <t>29,1; 44,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 29,98</t>
+          <t>15,6; 29,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,94; 52,42</t>
+          <t>35,26; 51,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,2; 48,52</t>
+          <t>33,69; 48,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,31; 34,04</t>
+          <t>17,33; 34,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,59; 46,53</t>
+          <t>35,73; 47,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 44,65</t>
+          <t>33,64; 44,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 28,85</t>
+          <t>18,21; 28,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 37,77</t>
+          <t>21,87; 37,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,5; 42,84</t>
+          <t>26,13; 44,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 22,93</t>
+          <t>5,15; 20,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 36,74</t>
+          <t>21,36; 37,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,65; 46,5</t>
+          <t>27,63; 46,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 20,27</t>
+          <t>6,12; 20,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,03; 35,67</t>
+          <t>23,93; 34,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,16; 42,68</t>
+          <t>29,12; 43,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 18,06</t>
+          <t>6,9; 17,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 31,25</t>
+          <t>21,81; 31,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 36,6</t>
+          <t>26,17; 36,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 19,04</t>
+          <t>8,31; 18,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,18; 34,4</t>
+          <t>24,32; 33,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 31,14</t>
+          <t>21,47; 31,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 27,54</t>
+          <t>15,81; 28,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,19; 31,42</t>
+          <t>24,31; 31,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,54; 32,69</t>
+          <t>25,59; 33,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 21,58</t>
+          <t>13,31; 21,75</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 29,02</t>
+          <t>17,34; 28,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 25,42</t>
+          <t>13,41; 24,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 17,36</t>
+          <t>7,54; 17,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,21; 35,0</t>
+          <t>22,52; 35,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,67; 24,61</t>
+          <t>13,96; 24,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 34,38</t>
+          <t>10,43; 34,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 30,1</t>
+          <t>21,27; 30,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 23,28</t>
+          <t>15,05; 22,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 26,99</t>
+          <t>10,66; 27,69</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,07; 31,16</t>
+          <t>13,07; 32,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,93; 37,99</t>
+          <t>20,29; 39,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 26,27</t>
+          <t>10,09; 26,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,75; 30,83</t>
+          <t>16,24; 32,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 30,73</t>
+          <t>13,68; 29,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 24,2</t>
+          <t>7,33; 22,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 28,83</t>
+          <t>16,24; 28,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 30,69</t>
+          <t>18,25; 30,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 21,61</t>
+          <t>9,75; 21,42</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,5</t>
+          <t>25,75; 31,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,21; 33,68</t>
+          <t>28,08; 33,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 18,75</t>
+          <t>13,66; 18,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,88; 35,76</t>
+          <t>30,13; 35,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 31,86</t>
+          <t>26,09; 32,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 25,29</t>
+          <t>17,48; 24,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,78; 32,74</t>
+          <t>28,45; 32,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,84; 31,86</t>
+          <t>27,91; 32,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,29; 21,05</t>
+          <t>16,44; 21,04</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25452; 39581</t>
+          <t>23948; 39659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26461; 41082</t>
+          <t>26240; 40780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17801; 32403</t>
+          <t>18466; 32532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35447; 51261</t>
+          <t>35933; 51206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28306; 43968</t>
+          <t>28187; 43370</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28385; 47205</t>
+          <t>26808; 47419</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65075; 86580</t>
+          <t>64314; 86402</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58318; 79626</t>
+          <t>59967; 80922</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50418; 75811</t>
+          <t>50361; 75424</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28172; 43740</t>
+          <t>28805; 44867</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29916; 46158</t>
+          <t>30385; 46165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14894; 28385</t>
+          <t>14774; 28220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34780; 50733</t>
+          <t>34125; 50250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37208; 54382</t>
+          <t>37753; 54078</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16541; 32533</t>
+          <t>16563; 32550</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65459; 88052</t>
+          <t>67616; 89736</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72714; 96674</t>
+          <t>72830; 96083</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35396; 54893</t>
+          <t>34637; 54974</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19441; 32539</t>
+          <t>18840; 32597</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15772; 26495</t>
+          <t>16158; 27561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3076; 11890</t>
+          <t>2672; 10839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18366; 31926</t>
+          <t>18559; 32605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21423; 34774</t>
+          <t>20661; 34740</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4097; 12946</t>
+          <t>3907; 13307</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39847; 61723</t>
+          <t>41404; 60520</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41199; 58306</t>
+          <t>39782; 59167</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8392; 20897</t>
+          <t>7987; 19922</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44235; 64417</t>
+          <t>44956; 65828</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59747; 81837</t>
+          <t>58505; 81064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19439; 41471</t>
+          <t>18111; 40734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55015; 78242</t>
+          <t>55317; 77102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44890; 65006</t>
+          <t>44826; 65005</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35145; 60116</t>
+          <t>34518; 62391</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104905; 136242</t>
+          <t>105419; 136110</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110413; 141327</t>
+          <t>110620; 142750</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58744; 94131</t>
+          <t>58062; 94866</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24904; 42822</t>
+          <t>25589; 42496</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19268; 34450</t>
+          <t>18169; 32733</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8704; 20733</t>
+          <t>9003; 20600</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31185; 49140</t>
+          <t>31615; 49347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19475; 35045</t>
+          <t>19879; 35496</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16667; 55901</t>
+          <t>16968; 56806</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61156; 86669</t>
+          <t>61256; 86902</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42816; 64707</t>
+          <t>41845; 62951</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29250; 76113</t>
+          <t>30070; 78106</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6955; 16581</t>
+          <t>6955; 17332</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11562; 23205</t>
+          <t>12392; 23823</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6311; 18101</t>
+          <t>6950; 18179</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11660; 22824</t>
+          <t>12020; 23934</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9088; 20841</t>
+          <t>9276; 19796</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5423; 17423</t>
+          <t>5280; 16094</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21382; 36682</t>
+          <t>20667; 36431</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23274; 39563</t>
+          <t>23532; 39390</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14149; 30449</t>
+          <t>13734; 30184</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173752; 212756</t>
+          <t>173903; 210373</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>188911; 225511</t>
+          <t>188024; 225213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87890; 123198</t>
+          <t>89786; 123911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213764; 255806</t>
+          <t>215518; 255938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>186066; 224581</t>
+          <t>183875; 225686</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>131688; 189080</t>
+          <t>130641; 182493</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>400285; 455411</t>
+          <t>395741; 455439</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>382660; 437949</t>
+          <t>383674; 441812</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>228763; 295724</t>
+          <t>230995; 295545</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>35,69%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>40,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 44,1</t>
+          <t>40,62; 57,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,58; 49,08</t>
+          <t>29,03; 44,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 31,14</t>
+          <t>23,11; 37,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,03; 57,05</t>
+          <t>28,22; 44,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,46; 43,79</t>
+          <t>32,48; 49,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 35,06</t>
+          <t>17,03; 31,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,79; 48,08</t>
+          <t>35,86; 47,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,93; 44,43</t>
+          <t>32,36; 43,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 31,46</t>
+          <t>21,76; 32,41</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>38,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>36,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>43,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,15; 48,52</t>
+          <t>34,8; 52,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,1; 44,21</t>
+          <t>34,2; 48,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,6; 29,81</t>
+          <t>16,72; 32,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 51,92</t>
+          <t>30,72; 46,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 48,25</t>
+          <t>29,29; 44,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,06</t>
+          <t>14,68; 28,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,73; 47,42</t>
+          <t>35,79; 47,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,64; 44,38</t>
+          <t>33,25; 44,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,21; 28,89</t>
+          <t>17,24; 28,41</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>29,59%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>34,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,87; 37,83</t>
+          <t>21,67; 37,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 44,57</t>
+          <t>27,2; 46,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 20,9</t>
+          <t>6,32; 20,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,36; 37,52</t>
+          <t>22,3; 38,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,63; 46,45</t>
+          <t>24,97; 44,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 20,84</t>
+          <t>4,89; 20,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,93; 34,97</t>
+          <t>24,08; 35,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,12; 43,31</t>
+          <t>29,21; 42,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 17,22</t>
+          <t>7,4; 18,32</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>26,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>31,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,88%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,81; 31,94</t>
+          <t>24,58; 34,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,17; 36,26</t>
+          <t>21,23; 31,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 18,7</t>
+          <t>14,91; 27,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 33,89</t>
+          <t>21,57; 32,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 31,14</t>
+          <t>26,72; 36,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 28,58</t>
+          <t>11,95; 20,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,31; 31,39</t>
+          <t>23,95; 31,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 33,02</t>
+          <t>25,71; 32,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 21,75</t>
+          <t>14,91; 22,85</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,47%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,75%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>22,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 28,8</t>
+          <t>21,81; 34,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,15</t>
+          <t>14,06; 25,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,25</t>
+          <t>10,79; 36,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 35,15</t>
+          <t>17,37; 28,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,96; 24,92</t>
+          <t>13,77; 24,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 34,93</t>
+          <t>7,52; 17,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,27; 30,18</t>
+          <t>21,22; 29,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,05; 22,65</t>
+          <t>15,18; 23,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 27,69</t>
+          <t>10,61; 26,0</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>21,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>28,12%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,07; 32,57</t>
+          <t>15,79; 31,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,29; 39,0</t>
+          <t>13,39; 28,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 26,39</t>
+          <t>7,11; 23,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,24; 32,33</t>
+          <t>12,83; 32,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,68; 29,19</t>
+          <t>19,15; 38,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 22,35</t>
+          <t>10,21; 28,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,24; 28,63</t>
+          <t>16,9; 29,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,25; 30,56</t>
+          <t>18,32; 30,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,42</t>
+          <t>10,47; 22,6</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>32,72%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>28,47%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>30,76%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,75; 31,15</t>
+          <t>29,99; 35,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,08; 33,64</t>
+          <t>26,14; 31,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 18,86</t>
+          <t>17,65; 25,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,13; 35,78</t>
+          <t>25,86; 31,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,09; 32,02</t>
+          <t>28,07; 33,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 24,41</t>
+          <t>14,44; 19,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,45; 32,75</t>
+          <t>28,66; 32,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,91; 32,14</t>
+          <t>27,89; 31,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 21,04</t>
+          <t>16,9; 21,46</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43633</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35511</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>32100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>33517</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24319</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43633</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35834</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62146</t>
+          <t>59965</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23948; 39659</t>
+          <t>36466; 51542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26240; 40780</t>
+          <t>28751; 44054</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18466; 32532</t>
+          <t>27965; 44941</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35933; 51206</t>
+          <t>25384; 40383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28187; 43370</t>
+          <t>26989; 40779</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26808; 47419</t>
+          <t>17525; 32265</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64314; 86402</t>
+          <t>64442; 85695</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59967; 80922</t>
+          <t>58943; 80126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50361; 75424</t>
+          <t>48727; 72574</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21605</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>35870</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>37800</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20991</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42319</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46220</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44122</t>
+          <t>42078</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28805; 44867</t>
+          <t>33683; 50443</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30385; 46165</t>
+          <t>38331; 54874</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14774; 28220</t>
+          <t>15280; 29245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34125; 50250</t>
+          <t>28406; 43457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37753; 54078</t>
+          <t>30582; 46505</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16563; 32550</t>
+          <t>14173; 27531</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67616; 89736</t>
+          <t>67726; 89209</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72830; 96083</t>
+          <t>71984; 96080</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34637; 54974</t>
+          <t>32396; 53387</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25007</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27900</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>25491</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>21166</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5819</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25007</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>27900</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>12947</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18840; 32597</t>
+          <t>18830; 33010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16158; 27561</t>
+          <t>20339; 34854</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2672; 10839</t>
+          <t>3599; 11802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18559; 32605</t>
+          <t>19210; 33403</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20661; 34740</t>
+          <t>15440; 27743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3907; 13307</t>
+          <t>2616; 10866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41404; 60520</t>
+          <t>41678; 60941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39782; 59167</t>
+          <t>39907; 57719</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7987; 19922</t>
+          <t>8167; 20225</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66066</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54019</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42252</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>54211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>70557</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29851</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66066</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54019</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75678</t>
+          <t>71087</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44956; 65828</t>
+          <t>55903; 78993</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58505; 81064</t>
+          <t>44316; 64788</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18111; 40734</t>
+          <t>30113; 56191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55317; 77102</t>
+          <t>44464; 66554</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44826; 65005</t>
+          <t>59733; 81915</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34518; 62391</t>
+          <t>21342; 37459</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105419; 136110</t>
+          <t>103845; 134573</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110620; 142750</t>
+          <t>111149; 139772</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58062; 94866</t>
+          <t>56725; 86957</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39979</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26708</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25931</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>33379</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>25732</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13899</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>39979</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26708</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>39732</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25589; 42496</t>
+          <t>30620; 48524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18169; 32733</t>
+          <t>20025; 36626</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9003; 20600</t>
+          <t>15989; 54568</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31615; 49347</t>
+          <t>25637; 41894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19879; 35496</t>
+          <t>18659; 33787</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16968; 56806</t>
+          <t>8925; 20761</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61256; 86902</t>
+          <t>61105; 85484</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41845; 62951</t>
+          <t>42181; 64382</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30070; 78106</t>
+          <t>28319; 69409</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17031</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13730</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9239</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>11251</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>17178</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>11541</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17031</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13730</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>21765</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6955; 17332</t>
+          <t>11690; 23646</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12392; 23823</t>
+          <t>9080; 19548</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6950; 18179</t>
+          <t>4853; 16085</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12020; 23934</t>
+          <t>6826; 17414</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9276; 19796</t>
+          <t>11698; 23254</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5280; 16094</t>
+          <t>7185; 19961</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20667; 36431</t>
+          <t>21512; 36965</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23532; 39390</t>
+          <t>23611; 38918</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13734; 30184</t>
+          <t>14516; 31331</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>152</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>234035</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>204410</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>141665</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>192302</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>205949</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>106420</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>234035</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>204410</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>153623</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>260043</t>
+          <t>247574</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173903; 210373</t>
+          <t>214532; 255127</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>188024; 225213</t>
+          <t>184234; 224780</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89786; 123911</t>
+          <t>121386; 172083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215518; 255938</t>
+          <t>174636; 212153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>183875; 225686</t>
+          <t>187930; 226716</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>130641; 182493</t>
+          <t>89619; 122860</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>395741; 455439</t>
+          <t>398665; 455051</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>383674; 441812</t>
+          <t>383325; 438725</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>230995; 295545</t>
+          <t>221162; 280805</t>
         </is>
       </c>
     </row>
